--- a/MS_Excel_Practical_Exam_Medium_Level (1).xlsx
+++ b/MS_Excel_Practical_Exam_Medium_Level (1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC18\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mohit DA-19\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF9E814-8B9B-41C4-AE4C-781A77F099DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0D4EA6-CEC8-42B6-BBB4-E3C889A42F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="805" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,8 +26,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="37" r:id="rId8"/>
-    <pivotCache cacheId="40" r:id="rId9"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="112">
   <si>
     <t>Total Questions: 30</t>
   </si>
@@ -400,6 +400,9 @@
   </si>
   <si>
     <t>2 Letter</t>
+  </si>
+  <si>
+    <t>Ans-26</t>
   </si>
 </sst>
 </file>
@@ -4086,7 +4089,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ACDF1E6B-8340-4964-B6E7-9A31FDF39A23}" name="PivotTable9" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ACDF1E6B-8340-4964-B6E7-9A31FDF39A23}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A27:B33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -4167,7 +4170,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C9EC214-E56E-4CF6-8759-E221653E4284}" name="PivotTable8" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C9EC214-E56E-4CF6-8759-E221653E4284}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A11:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField showAll="0"/>
@@ -4277,7 +4280,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{03456185-47DC-4D65-BB9A-313109007CCD}" name="PivotTable7" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{03456185-47DC-4D65-BB9A-313109007CCD}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B82:C87" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField showAll="0"/>
@@ -4345,7 +4348,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0C0CADED-3DF0-437D-B3EE-995CCC94F11E}" name="PivotTable6" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0C0CADED-3DF0-437D-B3EE-995CCC94F11E}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B74:C78" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField showAll="0"/>
@@ -5471,6 +5474,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5737,13 +5741,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1505E34F-E5C8-437A-BFD0-B9D5B600F43C}">
-  <dimension ref="A1:M155"/>
+  <dimension ref="A1:M200"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="54.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.90625" customWidth="1"/>
     <col min="5" max="6" width="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.90625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.26953125" bestFit="1" customWidth="1"/>
@@ -6102,7 +6106,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="10">
-        <f t="shared" ref="D15:D17" si="3">SUMIF($C$4:$C$9,C15,$K$4:$K$9)</f>
+        <f t="shared" ref="D15:D16" si="3">SUMIF($C$4:$C$9,C15,$K$4:$K$9)</f>
         <v>190200</v>
       </c>
     </row>
@@ -7015,22 +7019,22 @@
         <v>60480</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C145">
         <v>53100</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C146">
         <v>67200</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C147">
         <v>106200</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>66</v>
       </c>
@@ -7038,37 +7042,670 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B150" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B151" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B152" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B153" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B154" s="8">
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B155" s="8">
         <v>5</v>
       </c>
     </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>67</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C158" s="8">
+        <v>2</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B159" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C159" s="8">
+        <v>5</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E159">
+        <f>COUNTIFS(D158:D163,"North",B158:B163,"Laptop")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B160" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C160" s="8">
+        <v>3</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B161" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C161" s="8">
+        <v>1</v>
+      </c>
+      <c r="D161" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B162" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C162" s="8">
+        <v>4</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B163" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C163" s="8">
+        <v>2</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>68</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B168" s="8">
+        <v>46000</v>
+      </c>
+      <c r="C168" cm="1">
+        <f t="array" ref="C168:C173">ROUND(B168:B173,-3)</f>
+        <v>46000</v>
+      </c>
+      <c r="E168">
+        <v>16200</v>
+      </c>
+      <c r="F168" cm="1">
+        <f t="array" ref="F168:F173">ROUND(E168:E173,-3)</f>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B169" s="8">
+        <v>15000</v>
+      </c>
+      <c r="C169">
+        <v>15000</v>
+      </c>
+      <c r="E169">
+        <v>9000</v>
+      </c>
+      <c r="F169">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B170" s="8">
+        <v>18000</v>
+      </c>
+      <c r="C170">
+        <v>18000</v>
+      </c>
+      <c r="E170">
+        <v>6480</v>
+      </c>
+      <c r="F170">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B171" s="8">
+        <v>45000</v>
+      </c>
+      <c r="C171">
+        <v>45000</v>
+      </c>
+      <c r="E171">
+        <v>8100</v>
+      </c>
+      <c r="F171">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B172" s="8">
+        <v>15000</v>
+      </c>
+      <c r="C172">
+        <v>15000</v>
+      </c>
+      <c r="E172">
+        <v>7600</v>
+      </c>
+      <c r="F172">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B173" s="8">
+        <v>45000</v>
+      </c>
+      <c r="C173">
+        <v>45000</v>
+      </c>
+      <c r="E173">
+        <v>16200</v>
+      </c>
+      <c r="F173">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>69</v>
+      </c>
+      <c r="B176" t="s">
+        <v>4</v>
+      </c>
+      <c r="C176" t="s">
+        <v>5</v>
+      </c>
+      <c r="D176" t="s">
+        <v>6</v>
+      </c>
+      <c r="E176" t="s">
+        <v>7</v>
+      </c>
+      <c r="F176" t="s">
+        <v>8</v>
+      </c>
+      <c r="G176" t="s">
+        <v>9</v>
+      </c>
+      <c r="H176" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B177">
+        <v>301</v>
+      </c>
+      <c r="C177" t="s">
+        <v>11</v>
+      </c>
+      <c r="D177" t="s">
+        <v>12</v>
+      </c>
+      <c r="E177" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177">
+        <v>2</v>
+      </c>
+      <c r="G177">
+        <v>45000</v>
+      </c>
+      <c r="H177" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B178">
+        <v>302</v>
+      </c>
+      <c r="C178" t="s">
+        <v>15</v>
+      </c>
+      <c r="D178" t="s">
+        <v>16</v>
+      </c>
+      <c r="E178" t="s">
+        <v>17</v>
+      </c>
+      <c r="F178">
+        <v>5</v>
+      </c>
+      <c r="G178">
+        <v>15000</v>
+      </c>
+      <c r="H178" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B179">
+        <v>303</v>
+      </c>
+      <c r="C179" t="s">
+        <v>19</v>
+      </c>
+      <c r="D179" t="s">
+        <v>20</v>
+      </c>
+      <c r="E179" t="s">
+        <v>21</v>
+      </c>
+      <c r="F179">
+        <v>3</v>
+      </c>
+      <c r="G179">
+        <v>18000</v>
+      </c>
+      <c r="H179" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B180">
+        <v>304</v>
+      </c>
+      <c r="C180" t="s">
+        <v>23</v>
+      </c>
+      <c r="D180" t="s">
+        <v>24</v>
+      </c>
+      <c r="E180" t="s">
+        <v>13</v>
+      </c>
+      <c r="F180">
+        <v>1</v>
+      </c>
+      <c r="G180">
+        <v>45000</v>
+      </c>
+      <c r="H180" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B181">
+        <v>305</v>
+      </c>
+      <c r="C181" t="s">
+        <v>11</v>
+      </c>
+      <c r="D181" t="s">
+        <v>12</v>
+      </c>
+      <c r="E181" t="s">
+        <v>17</v>
+      </c>
+      <c r="F181">
+        <v>4</v>
+      </c>
+      <c r="G181">
+        <v>15000</v>
+      </c>
+      <c r="H181" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B182">
+        <v>306</v>
+      </c>
+      <c r="C182" t="s">
+        <v>15</v>
+      </c>
+      <c r="D182" t="s">
+        <v>16</v>
+      </c>
+      <c r="E182" t="s">
+        <v>13</v>
+      </c>
+      <c r="F182">
+        <v>2</v>
+      </c>
+      <c r="G182">
+        <v>45000</v>
+      </c>
+      <c r="H182" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>70</v>
+      </c>
+      <c r="B185" t="s">
+        <v>4</v>
+      </c>
+      <c r="C185" t="s">
+        <v>5</v>
+      </c>
+      <c r="D185" t="s">
+        <v>6</v>
+      </c>
+      <c r="E185" t="s">
+        <v>7</v>
+      </c>
+      <c r="F185" t="s">
+        <v>8</v>
+      </c>
+      <c r="G185" t="s">
+        <v>9</v>
+      </c>
+      <c r="H185" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B186">
+        <v>301</v>
+      </c>
+      <c r="C186" t="s">
+        <v>11</v>
+      </c>
+      <c r="D186" t="s">
+        <v>12</v>
+      </c>
+      <c r="E186" t="s">
+        <v>13</v>
+      </c>
+      <c r="F186">
+        <v>2</v>
+      </c>
+      <c r="G186">
+        <v>45000</v>
+      </c>
+      <c r="H186" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B187">
+        <v>302</v>
+      </c>
+      <c r="C187" t="s">
+        <v>15</v>
+      </c>
+      <c r="D187" t="s">
+        <v>16</v>
+      </c>
+      <c r="E187" t="s">
+        <v>17</v>
+      </c>
+      <c r="F187">
+        <v>5</v>
+      </c>
+      <c r="G187">
+        <v>15000</v>
+      </c>
+      <c r="H187" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B188">
+        <v>303</v>
+      </c>
+      <c r="C188" t="s">
+        <v>19</v>
+      </c>
+      <c r="D188" t="s">
+        <v>20</v>
+      </c>
+      <c r="E188" t="s">
+        <v>21</v>
+      </c>
+      <c r="F188">
+        <v>3</v>
+      </c>
+      <c r="G188">
+        <v>18000</v>
+      </c>
+      <c r="H188" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B189">
+        <v>304</v>
+      </c>
+      <c r="C189" t="s">
+        <v>23</v>
+      </c>
+      <c r="D189" t="s">
+        <v>24</v>
+      </c>
+      <c r="E189" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189">
+        <v>45000</v>
+      </c>
+      <c r="H189" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B190">
+        <v>305</v>
+      </c>
+      <c r="C190" t="s">
+        <v>11</v>
+      </c>
+      <c r="D190" t="s">
+        <v>12</v>
+      </c>
+      <c r="E190" t="s">
+        <v>17</v>
+      </c>
+      <c r="F190">
+        <v>4</v>
+      </c>
+      <c r="G190">
+        <v>15000</v>
+      </c>
+      <c r="H190" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B191">
+        <v>306</v>
+      </c>
+      <c r="C191" t="s">
+        <v>15</v>
+      </c>
+      <c r="D191" t="s">
+        <v>16</v>
+      </c>
+      <c r="E191" t="s">
+        <v>13</v>
+      </c>
+      <c r="F191">
+        <v>2</v>
+      </c>
+      <c r="G191">
+        <v>45000</v>
+      </c>
+      <c r="H191" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>71</v>
+      </c>
+      <c r="B195" t="s">
+        <v>31</v>
+      </c>
+      <c r="C195" t="s">
+        <v>32</v>
+      </c>
+      <c r="D195" t="s">
+        <v>33</v>
+      </c>
+      <c r="E195" t="s">
+        <v>34</v>
+      </c>
+      <c r="F195" t="s">
+        <v>35</v>
+      </c>
+      <c r="G195" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B196">
+        <v>1</v>
+      </c>
+      <c r="C196" t="s">
+        <v>37</v>
+      </c>
+      <c r="D196">
+        <v>78</v>
+      </c>
+      <c r="E196">
+        <v>82</v>
+      </c>
+      <c r="F196">
+        <v>85</v>
+      </c>
+      <c r="G196">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B197">
+        <v>2</v>
+      </c>
+      <c r="C197" t="s">
+        <v>38</v>
+      </c>
+      <c r="D197">
+        <v>88</v>
+      </c>
+      <c r="E197">
+        <v>91</v>
+      </c>
+      <c r="F197">
+        <v>90</v>
+      </c>
+      <c r="G197">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B198">
+        <v>3</v>
+      </c>
+      <c r="C198" t="s">
+        <v>39</v>
+      </c>
+      <c r="D198">
+        <v>65</v>
+      </c>
+      <c r="E198">
+        <v>70</v>
+      </c>
+      <c r="F198">
+        <v>72</v>
+      </c>
+      <c r="G198">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B199">
+        <v>4</v>
+      </c>
+      <c r="C199" t="s">
+        <v>40</v>
+      </c>
+      <c r="D199">
+        <v>92</v>
+      </c>
+      <c r="E199">
+        <v>89</v>
+      </c>
+      <c r="F199">
+        <v>94</v>
+      </c>
+      <c r="G199">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B200">
+        <v>5</v>
+      </c>
+      <c r="C200" t="s">
+        <v>41</v>
+      </c>
+      <c r="D200">
+        <v>55</v>
+      </c>
+      <c r="E200">
+        <v>60</v>
+      </c>
+      <c r="F200">
+        <v>58</v>
+      </c>
+      <c r="G200">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1"/>
   <autoFilter ref="A149:B155" xr:uid="{1505E34F-E5C8-437A-BFD0-B9D5B600F43C}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A150:B155">
       <sortCondition ref="B149:B155"/>
